--- a/Result/profitability/9955.xlsx
+++ b/Result/profitability/9955.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05125000000000004</v>
+        <v>0.19375</v>
       </c>
       <c r="N2" t="n">
-        <v>7.462499999999999</v>
+        <v>6.70125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.135</v>
+        <v>0.35375</v>
       </c>
       <c r="N3" t="n">
-        <v>7.4375</v>
+        <v>8.546250000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3175000000000001</v>
+        <v>0.44875</v>
       </c>
       <c r="N4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.147500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.32625</v>
+        <v>0.4787500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>8.32625</v>
+        <v>7.6775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4</v>
+        <v>0.51125</v>
       </c>
       <c r="N6" t="n">
-        <v>8.407500000000001</v>
+        <v>7.1775</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.49625</v>
+        <v>0.49875</v>
       </c>
       <c r="N7" t="n">
-        <v>8.362500000000001</v>
+        <v>7.67</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5012500000000001</v>
+        <v>0.6112500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>8.86375</v>
+        <v>7.32625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.56875</v>
       </c>
       <c r="N11" t="n">
-        <v>7.37125</v>
+        <v>7.371249999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.5312500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>7.04375</v>
+        <v>7.043749999999999</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>0.61875</v>
       </c>
       <c r="N13" t="n">
-        <v>7.65125</v>
+        <v>7.651249999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9955</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>402</v>
+      </c>
+      <c r="D75" t="n">
+        <v>397</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.42%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>122</v>
+      </c>
+      <c r="J75" t="n">
+        <v>96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>96</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.06125000000000005</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.22375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="X75" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.9037472446730346</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4.206896551724139</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.7984615384615384</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
